--- a/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,34</t>
+          <t>-0,62; 0,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,0</t>
+          <t>-1,2; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,09</t>
+          <t>-0,58; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; -0,07</t>
+          <t>-0,7; -0,07</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,19</t>
+          <t>-0,77; 1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,77</t>
+          <t>-1,15; 1,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,6</t>
+          <t>-0,36; 0,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,61</t>
+          <t>-0,36; 0,78</t>
         </is>
       </c>
     </row>
@@ -1099,27 +1099,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,41</t>
+          <t>-0,34; 0,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,7; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,26</t>
+          <t>-0,47; 0,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,11</t>
+          <t>-0,55; 0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,23</t>
+          <t>-0,33; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,53; 318,63</t>
+          <t>-85,87; 325,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,5</t>
+          <t>-0,62; 0,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-0,87; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-0,87; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,09</t>
+          <t>-0,59; 0,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; -0,07</t>
+          <t>-0,69; -0,07</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,19</t>
+          <t>-0,77; 1,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,12</t>
+          <t>-1,15; 0,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,76</t>
+          <t>-0,36; 0,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,78</t>
+          <t>-0,36; 0,61</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,42</t>
+          <t>-0,35; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,0</t>
+          <t>-0,66; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,27</t>
+          <t>-0,47; 0,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,11</t>
+          <t>-0,59; 0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,2</t>
+          <t>-0,31; 0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,01</t>
+          <t>-0,45; 0,01</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 325,29</t>
+          <t>-86,12; 345,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,71</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,36</t>
+          <t>-1,01; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>-1,01; 0,0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-0,74; 0,34</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>-1,06; 0,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 0,0</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,03</t>
+          <t>-0,53; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; -0,07</t>
+          <t>-0,72; -0,07</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-44,76%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,76; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,19; 0,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,79</t>
+          <t>-0,37; 0,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,61</t>
+          <t>-0,37; 0,61</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-0,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,41</t>
+          <t>-0,54; 0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,0</t>
+          <t>-0,58; 0,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,34</t>
+          <t>-0,36; 0,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,11</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,25</t>
+          <t>-0,33; 0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,01</t>
+          <t>-0,46; 0,01</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-35,14%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-64,92%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-35,14%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-64,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,12; 345,83</t>
+          <t>-85,53; 318,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,259 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.7796006245218465</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7140934222364215</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.7452876174266454</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,07</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,95</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,51</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.073115051183564</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>3.948720503402728</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>2.513051774498657</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 0,34</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,06; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 0,09</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; -0,07</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-44,76%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-72,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.286719621189268</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.286719621189268</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1362150560007915</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.3043216191222868</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.2146771505141901</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.2949204378607508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.014147033110569</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.013099392410211</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.7449635631345912</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.060838804172206</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.5296804522842689</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.7177980022536811</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3441549388201516</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.0929829464671604</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.07419058355443277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 1,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,19; 0,77</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,37; 0,6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,37; 0,61</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.44760229783759</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7279154746662616</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,15%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +860,261 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.01059181912671302</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.0005678049913839835</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.01804048954918351</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.016655420364327</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 0,26</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 0,11</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 0,41</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,65; 0,0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 0,23</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 0,01</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.7643996083434751</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.188424806012217</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>-0.3655683675539406</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.3668267606613699</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-35,14%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-64,92%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-18,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-78,67%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.194056298249643</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.7677857900915269</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>0.6017332283119378</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.6088290865331487</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-85,53; 318,63</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.02781021557103901</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.001490846758596501</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>0.09950634402182065</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.09186668599443676</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.09588398872008617</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1771223272813464</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.01382467654942477</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.1859332013643999</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.04261608285647104</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.1814595714908684</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.5416528545554643</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.5830227362881741</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.3581972753913636</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.6543236626218627</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.3293358333346145</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.4574243855916847</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.2632688069579128</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.108855903956096</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.4141885487552254</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.2348785292240095</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.007630030096038566</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.3514150750573984</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.6491538031195444</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.07435292055414336</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.184756591708373</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.7866948277350638</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.855291894365492</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>3.186261260810539</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1122,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
